--- a/SGC-CKN/Excel/70eaf3c0-62e9-4e15-aa2f-2712ea39394f_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-84_D800_16-03-2026.xlsx
+++ b/SGC-CKN/Excel/70eaf3c0-62e9-4e15-aa2f-2712ea39394f_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-84_D800_16-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="68">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa ( Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P11-84</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>KL-002</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha màu xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">22:05
@@ -106,9 +106,6 @@
 15/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -122,7 +119,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm san TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">01:00
@@ -160,7 +157,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">02:45
@@ -174,7 +171,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">03:22
@@ -191,7 +188,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">06:45
@@ -1186,24 +1183,24 @@
         <v>1.97</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="9">
         <v>-2.81</v>
@@ -1221,24 +1218,24 @@
         <v>6</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-12.81</v>
@@ -1256,24 +1253,24 @@
         <v>15.57</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="E14" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="16">
         <v>-18</v>
@@ -1291,24 +1288,24 @@
         <v>8.16</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="E15" s="21" t="s">
         <v>43</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>44</v>
       </c>
       <c r="F15" s="19">
         <v>-28.2</v>
@@ -1326,24 +1323,24 @@
         <v>26.89</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="E16" s="24" t="s">
         <v>47</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>48</v>
       </c>
       <c r="F16" s="22">
         <v>-35.82</v>
@@ -1361,24 +1358,24 @@
         <v>5.29</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="E17" s="27" t="s">
         <v>51</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>52</v>
       </c>
       <c r="F17" s="25">
         <v>-38.2</v>
@@ -1396,24 +1393,24 @@
         <v>1.01</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="E18" s="30" t="s">
         <v>56</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>57</v>
       </c>
       <c r="F18" s="28">
         <v>-41.46</v>
@@ -1431,12 +1428,12 @@
         <v>2.53</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1542,31 +1539,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1606,7 +1603,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1635,7 +1632,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1664,7 +1661,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1693,7 +1690,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1722,7 +1719,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1751,7 +1748,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1780,7 +1777,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1803,13 +1800,13 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>

--- a/SGC-CKN/Excel/70eaf3c0-62e9-4e15-aa2f-2712ea39394f_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-84_D800_16-03-2026.xlsx
+++ b/SGC-CKN/Excel/70eaf3c0-62e9-4e15-aa2f-2712ea39394f_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-84_D800_16-03-2026.xlsx
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGCT-KCN0003</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét pha màu xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">22:05
@@ -106,10 +106,13 @@
 15/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">00:40
@@ -143,9 +146,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
-  </si>
-  <si>
     <t xml:space="preserve">02:23
 16/03/2026</t>
   </si>
@@ -171,7 +171,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">03:22
@@ -1183,24 +1183,24 @@
         <v>1.97</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-2.81</v>
@@ -1218,24 +1218,24 @@
         <v>6</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-12.81</v>
@@ -1253,24 +1253,24 @@
         <v>15.57</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="16">
         <v>-18</v>
@@ -1288,18 +1288,18 @@
         <v>8.16</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>42</v>
@@ -1323,7 +1323,7 @@
         <v>26.89</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1358,7 +1358,7 @@
         <v>5.29</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1603,7 +1603,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1632,7 +1632,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1661,7 +1661,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1690,7 +1690,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1803,10 +1803,10 @@
         <v>67</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>

--- a/SGC-CKN/Excel/70eaf3c0-62e9-4e15-aa2f-2712ea39394f_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-84_D800_16-03-2026.xlsx
+++ b/SGC-CKN/Excel/70eaf3c0-62e9-4e15-aa2f-2712ea39394f_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-84_D800_16-03-2026.xlsx
@@ -23,7 +23,7 @@
     <t>Hạng mục</t>
   </si>
   <si>
-    <t>Thi công cọc khoan nhồi đại trà_lô đất ký hiệu CT-02</t>
+    <t>Thi công cọc khoan nhồi, tường vây cho các hạng mục_Lô CT-02</t>
   </si>
   <si>
     <t>Tên bộ phận</t>
@@ -115,7 +115,11 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">00:40
+    <t xml:space="preserve">23:01
+15/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:01
 16/03/2026</t>
   </si>
   <si>
@@ -164,21 +168,17 @@
 16/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">03:12
-16/03/2026</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">03:22
 16/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">06:36
+    <t>7</t>
+  </si>
+  <si>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:36
 16/03/2026</t>
   </si>
   <si>
@@ -1197,10 +1197,10 @@
         <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-2.81</v>
@@ -1209,13 +1209,13 @@
         <v>-12.81</v>
       </c>
       <c r="H12" s="9">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="I12" s="9">
         <v>10</v>
       </c>
       <c r="J12" s="12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1223,19 +1223,19 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F13" s="13">
         <v>-12.81</v>
@@ -1244,13 +1244,13 @@
         <v>-18</v>
       </c>
       <c r="H13" s="13">
-        <v>0.33</v>
+        <v>0.98</v>
       </c>
       <c r="I13" s="13">
         <v>5.19</v>
       </c>
       <c r="J13" s="12">
-        <v>15.57</v>
+        <v>5.28</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>30</v>
@@ -1258,19 +1258,19 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" s="16">
         <v>-18</v>
@@ -1293,7 +1293,7 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
@@ -1302,10 +1302,10 @@
         <v>27</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="19">
         <v>-28.2</v>
@@ -1328,19 +1328,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16" s="22">
         <v>-35.82</v>
@@ -1349,13 +1349,13 @@
         <v>-38.2</v>
       </c>
       <c r="H16" s="22">
-        <v>0.45</v>
+        <v>0.62</v>
       </c>
       <c r="I16" s="22">
         <v>2.38</v>
       </c>
-      <c r="J16" s="12">
-        <v>5.29</v>
+      <c r="J16" s="8">
+        <v>3.86</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1363,16 +1363,16 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E17" s="27" t="s">
         <v>51</v>
@@ -1384,13 +1384,13 @@
         <v>-41.46</v>
       </c>
       <c r="H17" s="25">
-        <v>3.23</v>
+        <v>0.23</v>
       </c>
       <c r="I17" s="25">
         <v>3.26</v>
       </c>
-      <c r="J17" s="8">
-        <v>1.01</v>
+      <c r="J17" s="12">
+        <v>13.97</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>52</v>
@@ -1615,13 +1615,13 @@
         <v>-12.81</v>
       </c>
       <c r="G3" s="9">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="H3" s="9">
         <v>10</v>
       </c>
       <c r="I3" s="12">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1632,7 +1632,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1644,13 +1644,13 @@
         <v>-18</v>
       </c>
       <c r="G4" s="13">
-        <v>0.33</v>
+        <v>0.98</v>
       </c>
       <c r="H4" s="13">
         <v>5.19</v>
       </c>
       <c r="I4" s="12">
-        <v>15.57</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1661,7 +1661,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1719,7 +1719,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1731,13 +1731,13 @@
         <v>-38.2</v>
       </c>
       <c r="G7" s="22">
-        <v>0.45</v>
+        <v>0.62</v>
       </c>
       <c r="H7" s="22">
         <v>2.38</v>
       </c>
-      <c r="I7" s="12">
-        <v>5.29</v>
+      <c r="I7" s="8">
+        <v>3.86</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1748,7 +1748,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1760,13 +1760,13 @@
         <v>-41.46</v>
       </c>
       <c r="G8" s="25">
-        <v>3.23</v>
+        <v>0.23</v>
       </c>
       <c r="H8" s="25">
         <v>3.26</v>
       </c>
-      <c r="I8" s="8">
-        <v>1.01</v>
+      <c r="I8" s="12">
+        <v>13.97</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1818,13 +1818,13 @@
         <v>-49.88</v>
       </c>
       <c r="G10" s="33">
-        <v>11.47</v>
+        <v>8.62</v>
       </c>
       <c r="H10" s="33">
         <v>48.88</v>
       </c>
       <c r="I10" s="33">
-        <v>4.26</v>
+        <v>5.67</v>
       </c>
     </row>
   </sheetData>
